--- a/input/old/Metadata _Is the system open__SW_01_01_SYS_IS_OPEN.xlsx
+++ b/input/old/Metadata _Is the system open__SW_01_01_SYS_IS_OPEN.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16.01.2026 at 17:05 by ILIYAR</t>
+          <t>16.01.2026 at 17:05 by REDACTED</t>
         </is>
       </c>
     </row>
